--- a/원료_추가노트.xlsx
+++ b/원료_추가노트.xlsx
@@ -12,6 +12,8 @@
     <sheet name="신규 원료 카드" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="제품 목록" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="제품 해부" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="출시 비용·절차" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="정오표" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'원료 색인'!$A$4:$I$319</definedName>
@@ -24,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +78,11 @@
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF0563C1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="22">
@@ -212,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -278,6 +285,19 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -644,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -654,7 +674,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>원료 추가노트 — 1권(원료 마스터) 증보</t>
+          <t>원료 추가노트 — 1·2권 증보</t>
         </is>
       </c>
     </row>
@@ -728,34 +748,58 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>쌓는 루프</t>
+          <t>출시 비용·절차</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>① 제품 전성분 사진 → Claude에게 질문  ② 1권에 있으면 #번호, 없으면 N번호 카드 추가  ③ 라벨 표기가 1권 이름과 다르면 별칭 추가  ④ 재생성  ⑤ 손으로 '내 메모'</t>
+          <t>등록·자격·인증·품질검사·OEM·예산을 출처로 재검증한 표(확인/정정/미확인). 2권 '개발→창업 워크플로우'의 증보.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>전성분 읽기 요령</t>
+          <t>정오표</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1% 초과 성분은 많은 순서, 1% 이하는 순서 무관. 함량(ppm) 표기 = 마케팅 강조 성분. 원료 1개가 성분 여러 개로(부산물·용매) 적히기도 한다.</t>
+          <t>제본한 1·2권에서 고치거나 보충할 내용을 쪽 번호와 함께.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>쌓는 루프</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>① 제품 전성분 사진 → Claude에게 질문  ② 1권에 있으면 #번호, 없으면 N번호 카드 추가  ③ 라벨 표기가 1권 이름과 다르면 별칭 추가  ④ 재생성  ⑤ 손으로 '내 메모'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>전성분 읽기 요령</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1% 초과 성분은 많은 순서, 1% 이하는 순서 무관. 함량(ppm) 표기 = 마케팅 강조 성분. 원료 1개가 성분 여러 개로(부산물·용매) 적히기도 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>⚠</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>%·규제 수치는 교육용 정리(추정 포함). 제조·판매 전 식약처 최신 고시·공급사 TDS로 재확인.</t>
         </is>
@@ -18904,4 +18948,984 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>출시 비용·절차 — 조사 재검증 (2026-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>히어로 기준 = 50mL 크림 × MOQ 1,000개, OEM 위탁 + 책임판매업. 금액은 2026-10 공개 자료 기반 추정 — 공장·시험기관 견적으로 확정.  판정: 확인 = 출처로 맞음 · 정정 = 조사 내용이 틀려 고침 · 미확인 = 공개 근거 부족, 견적·문의로 확정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>확인된 내용</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>금액(추정)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>등록·자격</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>등록·자격</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>책임판매관리자 자격</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>이공계 학사(화학공학 포함)는 경력 없이 자격. 상시근로자 10명 이하면 대표 본인이 겸직 가능(시행규칙 제8조). 화학공학 '전문학사'는 경력 1년 필요.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="inlineStr">
+        <is>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1301&amp;ccfNo=2&amp;cciNo=2&amp;cnpClsNo=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>등록·자격</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>책임판매업 등록 수수료</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>전자민원 27,000원 / 방문·우편 30,000원. 처리기간 10일. 의약품안전나라 신청.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>27,000원</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>https://www.gov.kr/mw/AA020InfoCappView.do?HighCtgCD=A09006&amp;CappBizCD=14710000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>등록·자격</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>등록면허세</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>수수료와 별도(지방세법). 영수증을 의약품안전나라에 올려야 등록증 출력. 종별·인구별 차등 — 책임판매업이 몇 종인지 공식 확인 못 함 → 관할 구청·위택스 문의.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>약 1.8만~6.75만원(미확정)</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F8" s="36" t="inlineStr">
+        <is>
+          <t>https://www.ansan.go.kr/sangnokgu/common/cntnts/selectContents.do?cntnts_id=C0000113</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>등록·자격</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>책임판매관리자 의무 교육</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>최초 = 등록 후 6개월 이내, 이후 매년 1회(연도 기준, 12/31까지). 미이수 시 과태료 50만원. 온라인 6시간 과정 기준 288분 이상 수강 + 평가 60점.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>교육비 별도</t>
+        </is>
+      </c>
+      <c r="E9" s="38" t="inlineStr">
+        <is>
+          <t>정정</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>https://kcia.or.kr/home/edu/edu_faq.php?sse=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>등록·자격</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>통신판매업 신고</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>스마트스토어·자사몰 판매 시 필요(조사에서 누락). 간이과세자 등 면제 조건 있음 — 확인 필요.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>천연·유기농화장품 정부 인증</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>화장품법 개정 2025.1.31 공포 → 2025.8.1 시행으로 식약처 인증제 폐지, 민간 자율로 전환. 이제 '천연·유기농화장품 표시·광고 안내서'(식약처+업계) 기준 충족 + 실증자료, 또는 COSMOS 등 민간 인증. KCL 114만원은 폐지 전 인증심사비.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>정부 인증비 0원(제도 없음)</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="inlineStr">
+        <is>
+          <t>정정</t>
+        </is>
+      </c>
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>https://www.cncnews.co.kr/news/article.html?no=9757</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>해외 비건 인증(EVE 등)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>공개 가격 없음. EVE 국내 파트너 계약이 2024년 해지 통보 → 현재 국내 창구 재확인 필요. 다도기는 비건 소구 계획 없음.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>견적 필요</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F13" s="36" t="inlineStr">
+        <is>
+          <t>https://kyeonggi.com/article/20240415580196</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>품질검사</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>품질검사</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>제조번호별 품질검사 의무</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>책임판매업자 의무는 맞음. 단, 외부 기관 필수 아님 — 제조업자에게 받은 제품표준서·품질관리기록서 보관, 지정기관 위탁 결과 등으로 갈음 가능(시행규칙 제11·12조). CGMP 공장 시험실이 로트별 검사하는 경우가 많아 견적 포함 여부 확인.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>0원~수십만원(포함 여부)</t>
+        </is>
+      </c>
+      <c r="E15" s="38" t="inlineStr">
+        <is>
+          <t>정정</t>
+        </is>
+      </c>
+      <c r="F15" s="36" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/LSW//lsLawLinkInfo.do?chrClsCd=010202&amp;lsJoLnkSeq=1000294907&amp;lsId=008741&amp;print=print</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>품질검사</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>유통화장품 안전관리 기준 항목</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>중금속 6종: 납 20·니켈 10(눈화장 35)·비소 10·수은 1·안티몬 10·카드뮴 5 µg/g 이하(조사의 '5종'은 니켈 누락). 다이옥산·프탈레이트 각 100ppm 이하. 미생물·내용량·pH 등.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="38" t="inlineStr">
+        <is>
+          <t>정정</t>
+        </is>
+      </c>
+      <c r="F16" s="36" t="inlineStr">
+        <is>
+          <t>https://www.metroseoul.co.kr/article/20230407500005</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>품질검사</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>방부력·안정성 시험</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>공개 가격 없음 → 시험기관 견적(KTR 뷰티소비재센터 02-2092-3722). 조사의 '30~50만원'은 근거 미확인.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>견적 필요</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F17" s="36" t="inlineStr">
+        <is>
+          <t>https://www.ktr.or.kr/test-evaluation/cosmetic/contentsid/308/index.do</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>품질검사</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>양산 → 로트 샘플 검사 → 적합 판정 후 출고. 맞음.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="35" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F18" s="36" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/LSW//lsLawLinkInfo.do?chrClsCd=010202&amp;lsJoLnkSeq=1000294907&amp;lsId=008741&amp;print=print</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>MOQ 1,000개</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>'대중적 최소수량'은 과장. 기초화장품 기준 SKU당 보통 3,000~5,000개, 1,000개는 건별 상담·소량 전문사(예: 연제 2,000~3,000개, 스피드코스 1,000개~). 소량일수록 개당 단가↑.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="38" t="inlineStr">
+        <is>
+          <t>정정</t>
+        </is>
+      </c>
+      <c r="F20" s="36" t="inlineStr">
+        <is>
+          <t>https://signal.nextpangaea.com/blog/private-label-cost-moq/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>매칭 플랫폼</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>셀프코스(selfcos — 조사의 '셀코스'), 팩토스퀘어는 실재. '매치메이드'는 확인 못 함.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="38" t="inlineStr">
+        <is>
+          <t>정정</t>
+        </is>
+      </c>
+      <c r="F21" s="36" t="inlineStr">
+        <is>
+          <t>https://www.selfcos.com/index/notice_view/176</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>계약 조항</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>처방 소유권·납기 지연 배상·부적합 재생산·NDA·계약금/잔금 50:50은 권고로는 타당하나 업계 표준이란 근거 없음 → 변호사 검토 권장.</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>내용물</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>크림 g당 5~6원(셀프코스 2023, 5,000개 기준) × 50g, 소량 할증 감안.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>30~60만원</t>
+        </is>
+      </c>
+      <c r="E24" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F24" s="36" t="inlineStr">
+        <is>
+          <t>https://www.selfcos.com/index/notice_view/176</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>임가공·충진</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>개당 약 500원 안팎(셀프코스 2023).</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>50~80만원</t>
+        </is>
+      </c>
+      <c r="E25" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F25" s="36" t="inlineStr">
+        <is>
+          <t>https://www.selfcos.com/index/notice_view/176</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>용기(50mL 자)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>개당 500~2,000원(사양·후가공에 따라).</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>50~200만원</t>
+        </is>
+      </c>
+      <c r="E26" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F26" s="36" t="inlineStr">
+        <is>
+          <t>https://www.selfcos.com/index/notice_view/176</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>단상자</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>개당 250~700원 + 인쇄 판비.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>25~70만원</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F27" s="36" t="inlineStr">
+        <is>
+          <t>https://www.selfcos.com/index/notice_view/176</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>라벨</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>소량 스티커 인쇄.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>5~20만원</t>
+        </is>
+      </c>
+      <c r="E28" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>수수료 + 등록면허세(최초 1회).</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>5~10만원</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F29" s="36" t="inlineStr">
+        <is>
+          <t>https://www.gov.kr/mw/AA020InfoCappView.do?HighCtgCD=A09006&amp;CappBizCD=14710000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>합계(생산 기준)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>교차확인: 5,000개 기준 개당 원가 1,800~3,900원(내용물+용기+단상자) → 1,000개는 더 높음. 조사의 300~600만원은 큰 틀에서 타당.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>약 170~450만원</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F30" s="36" t="inlineStr">
+        <is>
+          <t>https://signal.nextpangaea.com/blog/private-label-cost-moq/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>조사에서 빠진 비용</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>샘플 수정 차수, 디자인 외주, 바코드(GS1) 가입, 통신판매업 신고, 택배·포장재, 생산물배상책임보험(선택).</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>별도</t>
+        </is>
+      </c>
+      <c r="E31" s="37" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>미팅 질문</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>미팅 질문</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>공장에 꼭 물을 3가지</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>① 로트별 품질검사(성적서)가 견적에 포함인가 ② 1,000개 수락 여부와 할증 ③ 샘플 수정 몇 차까지 무료인가.</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId18"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>정오표 — 제본한 1·2권에 덧붙일 정정·보충</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>쪽 = 인쇄본 PDF 쪽 번호. 정정 = 책 내용이 틀림 · 보충 = 맞지만 빠진 정보. 책에 포스트잇으로 붙이거나 이 표를 출력해 끼워 두기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>권</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>쪽</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>책에 적힌 것</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>정정·보충</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2권</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>189·192·198·212</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>교재 이론 목차 · 시험 핵심개념 · 시험→사업 활용</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>천연·유기농 정의·인증 조항 2025.1.31 삭제</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2025.1.31은 공포일. 시행은 2025.8.1(공포 후 6개월). 기존 인증은 유효기간까지 인정, 이후 민간 표시·광고 안내서·COSMOS 등 민간 인증으로.</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="inlineStr">
+        <is>
+          <t>보충</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>https://www.cncnews.co.kr/news/article.html?no=9757</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2권</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>189·198·212</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>교재 이론 목차 · 시험 핵심개념 · 시험→사업 활용</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>책임판매관리자 교육 매년 4~8시간 · 최초 6개월 이내</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>미이수 시 과태료 50만원. 보수교육은 연도 기준(12/31까지 수료해야 그 해 인정).</t>
+        </is>
+      </c>
+      <c r="F6" s="29" t="inlineStr">
+        <is>
+          <t>보충</t>
+        </is>
+      </c>
+      <c r="G6" s="36" t="inlineStr">
+        <is>
+          <t>https://kcia.or.kr/home/edu/edu_faq.php?sse=5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/원료_추가노트.xlsx
+++ b/원료_추가노트.xlsx
@@ -22409,7 +22409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22909,63 +22909,55 @@
     <row r="23">
       <c r="A23" s="38" t="inlineStr">
         <is>
-          <t>예산(50mL×1,000)</t>
+          <t>OEM·ODM 선택</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>예산(50mL×1,000)</t>
+          <t>OEM·ODM 선택</t>
         </is>
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>내용물</t>
+          <t>OEM vs ODM</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>크림 g당 5~6원(셀프코스 2023, 5,000개 기준) × 50g, 소량 할증 감안.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>30~60만원</t>
-        </is>
-      </c>
-      <c r="E24" s="43" t="inlineStr">
-        <is>
-          <t>미확인</t>
+          <t>OEM = 브랜드가 처방을 주고 제조사는 생산만. ODM = 제조사가 처방 개발·생산까지, 브랜드는 기획·판매. 두 방식 모두 브랜드(상표)는 주문자 소유. 국내는 1990년대 OEM으로 시작해 연구소를 키운 ODM(코스맥스·한국콜마 등)으로 발전.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="41" t="inlineStr">
+        <is>
+          <t>확인</t>
         </is>
       </c>
       <c r="F24" s="42" t="inlineStr">
         <is>
-          <t>https://www.selfcos.com/index/notice_view/176</t>
+          <t>https://koreascience.kr/article/JAKO202019962558991.pdf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>예산(50mL×1,000)</t>
+          <t>OEM·ODM 선택</t>
         </is>
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>임가공·충진</t>
+          <t>기성 처방 공유</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>개당 약 500원 안팎(셀프코스 2023).</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>50~80만원</t>
-        </is>
-      </c>
+          <t>인디·중소 브랜드는 대부분 생산시설이 없어 ODM에 의존하고, 경쟁 브랜드들이 같은 ODM 라인을 쓰는 사례가 늘었다는 보도. 단 '같은 처방을 여러 브랜드에 판다'의 실태·비율은 공개 근거를 못 찾음 — 제조사에 '이 처방을 다른 브랜드에도 공급하나' 직접 질문.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="43" t="inlineStr">
         <is>
           <t>미확인</t>
@@ -22973,31 +22965,27 @@
       </c>
       <c r="F25" s="42" t="inlineStr">
         <is>
-          <t>https://www.selfcos.com/index/notice_view/176</t>
+          <t>https://v.daum.net/v/20241029070117738</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>예산(50mL×1,000)</t>
+          <t>OEM·ODM 선택</t>
         </is>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>용기(50mL 자)</t>
+          <t>처방 소유권</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>개당 500~2,000원(사양·후가공에 따라).</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>50~200만원</t>
-        </is>
-      </c>
+          <t>ODM 구조에선 별도 조항이 없으면 처방·시험자료 권리가 제조사에 남을 수 있다(업계 해설). 'OEM인 줄 알았는데 ODM 구조'면 공장을 옮길 때 재개발. → 계약서에 처방 귀속·처방서 인도·독점 공급 기간 명시. 법적 표준은 없음 — 변호사 검토.</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="43" t="inlineStr">
         <is>
           <t>미확인</t>
@@ -23005,99 +22993,66 @@
       </c>
       <c r="F26" s="42" t="inlineStr">
         <is>
-          <t>https://www.selfcos.com/index/notice_view/176</t>
+          <t>https://www.cosmeticsbusiness.com/what-is-the-difference-between-oem-odm--160962</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>예산(50mL×1,000)</t>
+          <t>OEM·ODM 선택</t>
         </is>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>단상자</t>
+          <t>다도기 히어로 = OEM형</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>개당 250~700원 + 인쇄 판비.</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>25~70만원</t>
-        </is>
-      </c>
+          <t>처방(sebum-calm-cream v2)을 직접 보유 → 내 처방을 들고 가는 OEM. 협의할 것: ① 스케일업 수정본도 내 소유 ② 원료 지정 유지(몬타노브 68 등 — 공장 재고 원료로 대체 금지, 말라세지아 세이프 원칙) ③ 안정성 데이터 비용·소유 ④ 특수 원료 지정 시 단가·MOQ 상승 여부.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="43" t="inlineStr">
         <is>
           <t>미확인</t>
         </is>
       </c>
-      <c r="F27" s="42" t="inlineStr">
-        <is>
-          <t>https://www.selfcos.com/index/notice_view/176</t>
-        </is>
-      </c>
+      <c r="F27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>OEM·ODM 선택</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>라벨로 제조 구조 읽기</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>포장에 영업자 상호·주소 기재 의무(화장품법 제10조). '화장품제조업자'·'화장품책임판매업자'는 구분 기재, 같은 회사면 '화장품제조업자 및 화장품책임판매업자'로 한꺼번에(시행규칙 별표4) — P002가 이 경우((주)웰코스). 10mL·10g 이하 소량은 책임판매업자 상호만 가능(식약처 운영방침).</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="41" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F28" s="42" t="inlineStr">
+        <is>
+          <t>https://www.nepla.ai/law/%ED%99%94%EC%9E%A5%ED%92%88%EB%B2%95-%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="38" t="inlineStr">
+        <is>
           <t>예산(50mL×1,000)</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>라벨</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>소량 스티커 인쇄.</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>5~20만원</t>
-        </is>
-      </c>
-      <c r="E28" s="43" t="inlineStr">
-        <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>예산(50mL×1,000)</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>등록</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>수수료 + 등록면허세(최초 1회).</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>5~10만원</t>
-        </is>
-      </c>
-      <c r="E29" s="41" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="F29" s="42" t="inlineStr">
-        <is>
-          <t>https://www.gov.kr/mw/AA020InfoCappView.do?HighCtgCD=A09006&amp;CappBizCD=14710000002</t>
         </is>
       </c>
     </row>
@@ -23109,27 +23064,27 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>합계(생산 기준)</t>
+          <t>내용물</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>교차확인: 5,000개 기준 개당 원가 1,800~3,900원(내용물+용기+단상자) → 1,000개는 더 높음. 조사의 300~600만원은 큰 틀에서 타당.</t>
+          <t>크림 g당 5~6원(셀프코스 2023, 5,000개 기준) × 50g, 소량 할증 감안.</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>약 170~450만원</t>
-        </is>
-      </c>
-      <c r="E30" s="41" t="inlineStr">
-        <is>
-          <t>확인</t>
+          <t>30~60만원</t>
+        </is>
+      </c>
+      <c r="E30" s="43" t="inlineStr">
+        <is>
+          <t>미확인</t>
         </is>
       </c>
       <c r="F30" s="42" t="inlineStr">
         <is>
-          <t>https://signal.nextpangaea.com/blog/private-label-cost-moq/</t>
+          <t>https://www.selfcos.com/index/notice_view/176</t>
         </is>
       </c>
     </row>
@@ -23141,17 +23096,17 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>조사에서 빠진 비용</t>
+          <t>임가공·충진</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>샘플 수정 차수, 디자인 외주, 바코드(GS1) 가입, 통신판매업 신고, 택배·포장재, 생산물배상책임보험(선택).</t>
+          <t>개당 약 500원 안팎(셀프코스 2023).</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>별도</t>
+          <t>50~80만원</t>
         </is>
       </c>
       <c r="E31" s="43" t="inlineStr">
@@ -23159,41 +23114,230 @@
           <t>미확인</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="F31" s="42" t="inlineStr">
+        <is>
+          <t>https://www.selfcos.com/index/notice_view/176</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="inlineStr">
-        <is>
-          <t>미팅 질문</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>용기(50mL 자)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>개당 500~2,000원(사양·후가공에 따라).</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>50~200만원</t>
+        </is>
+      </c>
+      <c r="E32" s="43" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F32" s="42" t="inlineStr">
+        <is>
+          <t>https://www.selfcos.com/index/notice_view/176</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>단상자</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>개당 250~700원 + 인쇄 판비.</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>25~70만원</t>
+        </is>
+      </c>
+      <c r="E33" s="43" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F33" s="42" t="inlineStr">
+        <is>
+          <t>https://www.selfcos.com/index/notice_view/176</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>라벨</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>소량 스티커 인쇄.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>5~20만원</t>
+        </is>
+      </c>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>수수료 + 등록면허세(최초 1회).</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>5~10만원</t>
+        </is>
+      </c>
+      <c r="E35" s="41" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F35" s="42" t="inlineStr">
+        <is>
+          <t>https://www.gov.kr/mw/AA020InfoCappView.do?HighCtgCD=A09006&amp;CappBizCD=14710000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>합계(생산 기준)</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>교차확인: 5,000개 기준 개당 원가 1,800~3,900원(내용물+용기+단상자) → 1,000개는 더 높음. 조사의 300~600만원은 큰 틀에서 타당.</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>약 170~450만원</t>
+        </is>
+      </c>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F36" s="42" t="inlineStr">
+        <is>
+          <t>https://signal.nextpangaea.com/blog/private-label-cost-moq/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>예산(50mL×1,000)</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>조사에서 빠진 비용</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>샘플 수정 차수, 디자인 외주, 바코드(GS1) 가입, 통신판매업 신고, 택배·포장재, 생산물배상책임보험(선택).</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>별도</t>
+        </is>
+      </c>
+      <c r="E37" s="43" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="38" t="inlineStr">
+        <is>
           <t>미팅 질문</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>미팅 질문</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>공장에 꼭 물을 3가지</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>① 로트별 품질검사(성적서)가 견적에 포함인가 ② 1,000개 수락 여부와 할증 ③ 샘플 수정 몇 차까지 무료인가.</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="41" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="41" t="inlineStr">
         <is>
           <t>확인</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A19:F19"/>
@@ -23201,7 +23345,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId1"/>
@@ -23219,9 +23363,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
